--- a/Тест2/280.xlsx
+++ b/Тест2/280.xlsx
@@ -126,19 +126,19 @@
     <t xml:space="preserve">Qo'ldan surtma olish uchun nima ishlatiladi?</t>
   </si>
   <si>
-    <t xml:space="preserve">Metall qirg'ich yoki pichoq</t>
+    <t xml:space="preserve">Metall qirg'ich yoki o'tkir pichoq</t>
   </si>
   <si>
     <t xml:space="preserve">Steril paxta tamponi yoki surtma tayoqchasi</t>
   </si>
   <si>
-    <t xml:space="preserve">Quruq mato yoki paxta tolasi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yuvilmagan latta yoki qo'lqop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oddiy gazeta qog'ozi yoki salfetka</t>
+    <t xml:space="preserve">Quruq mato yoki oddiy paxta tolasi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yuvilmagan latta yoki ishlatilgan qo'lqop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oddiy gazeta qog'ozi yoki qog'oz salfetka</t>
   </si>
   <si>
     <t xml:space="preserve">To'g'ri javob: Steril paxta tamponi yoki surtma tayoqchasi. Surtma olish uchun steril paxta tamponi yoki maxsus surtma tayoqchasi ishlatiladi. Manba: Mavzu materiali (280.docx).</t>
